--- a/output/tables/report_tables.xlsx
+++ b/output/tables/report_tables.xlsx
@@ -15,27 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
-  <si>
-    <t xml:space="preserve">Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max</t>
   </si>
   <si>
     <t xml:space="preserve">close</t>
@@ -44,79 +44,58 @@
     <t xml:space="preserve">volume</t>
   </si>
   <si>
-    <t xml:space="preserve">returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing_Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing_Percentage</t>
+    <t xml:space="preserve">return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing_percentage</t>
   </si>
   <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
+    <t xml:space="preserve">open</t>
+  </si>
+  <si>
     <t xml:space="preserve">high</t>
   </si>
   <si>
     <t xml:space="preserve">low</t>
   </si>
   <si>
-    <t xml:space="preserve">open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_close</t>
   </si>
   <si>
-    <t xml:space="preserve">return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key_Metric_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key_Metric_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dự báo mức giá trung bình (Mean Forecast)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMSE: 2,016.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPE: 2.19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMSE: 2,099.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPE: 2.29%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMA(0,0)-GARCH(1,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dự báo mức độ biến động (Volatility Forecast)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC: -5.5589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIC: -5.5508</t>
+    <t xml:space="preserve">weekday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">provisional_conclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holdout leader: ARIMAX (Lagged); rolling-CV leader among evaluated models: ETS Damped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holdout and rolling-CV evidence do not identify one universal winner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditional volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisional candidate: eGARCH-Student-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results are provisional until final clean-data rerun and distribution limitations remain</t>
   </si>
   <si>
     <t xml:space="preserve">Parameter</t>
@@ -555,22 +534,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2960</v>
+        <v>2787</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>40914.67631572</v>
+        <v>40798.2489608912</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>21598.685546875</v>
+        <v>21344.078125</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>34871.6976290608</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>6955.4501953125</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>129855.7265625</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>34715.0516431167</v>
       </c>
     </row>
     <row r="3">
@@ -578,22 +557,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2960</v>
+        <v>2787</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3943219.04222973</v>
+        <v>4187990.08432006</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2738958</v>
+        <v>2913864</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>9925516.62641437</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>53113</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>415709889</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>9680991.30402982</v>
       </c>
     </row>
     <row r="4">
@@ -601,22 +580,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2959</v>
+        <v>2786</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.000916064737785308</v>
+        <v>0.000836523798965639</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.0699115588048182</v>
+        <v>0.0165819991700203</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0925666210928712</v>
+        <v>-0.0724755992970323</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.0161135192920815</v>
+        <v>0.0885296265337523</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +638,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
@@ -670,7 +649,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
@@ -681,7 +660,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
@@ -692,7 +671,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
@@ -725,35 +704,24 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.035880875493362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0337837837837838</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.0337837837837838</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -767,66 +735,42 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="58.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="85.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="88.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -849,50 +793,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.00110071173925282</v>
+        <v>0.00115144547359355</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.000252879085735288</v>
+        <v>0.00026485051915453</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.35271954599297</v>
+        <v>4.34752960752826</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0000134459110834317</v>
+        <v>0.0000137679489848885</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.00000798014158168426</v>
+        <v>0.00000980701419613725</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.000000495539153347049</v>
+        <v>0.000000479286724104228</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.103957735294</v>
+        <v>20.4616854649297</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -900,16 +844,16 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.0672589766030614</v>
+        <v>0.0783725569418704</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.00469443114152317</v>
+        <v>0.00538531877837568</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.3273965631624</v>
+        <v>14.5530023694362</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -917,16 +861,16 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.902142555700691</v>
+        <v>0.886137081631381</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.00556755320323066</v>
+        <v>0.00659940568331388</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>162.035731455105</v>
+        <v>134.275285405156</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -934,10 +878,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8228.43921764548</v>
+        <v>7675.66903100474</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -945,10 +889,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-5.55893154284926</v>
+        <v>-5.50730009404504</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -956,10 +900,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-5.55083068897646</v>
+        <v>-5.49878270401727</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>

--- a/output/tables/report_tables.xlsx
+++ b/output/tables/report_tables.xlsx
@@ -6,10 +6,10 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Thong_Ke_Mo_Ta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Missing_Values" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="So_Sanh_Mo_Hinh" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tham_So_GARCH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Price forecast</t>
   </si>
   <si>
-    <t xml:space="preserve">Holdout leader: ARIMAX (Lagged); rolling-CV leader among evaluated models: ETS Damped</t>
+    <t xml:space="preserve">Holdout leader: ETS Damped; rolling-CV leader among evaluated models: Naive</t>
   </si>
   <si>
     <t xml:space="preserve">Holdout and rolling-CV evidence do not identify one universal winner</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">Conditional volatility</t>
   </si>
   <si>
-    <t xml:space="preserve">Provisional candidate: eGARCH-Student-t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results are provisional until final clean-data rerun and distribution limitations remain</t>
+    <t xml:space="preserve">Balanced candidate: eGARCH-Student-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution fit remains a limitation</t>
   </si>
   <si>
     <t xml:space="preserve">Parameter</t>
@@ -736,8 +736,8 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="85.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="88.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="75.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="68.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/output/tables/report_tables.xlsx
+++ b/output/tables/report_tables.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -98,19 +98,28 @@
     <t xml:space="preserve">Distribution fit remains a limitation</t>
   </si>
   <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StdError</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr_z</t>
+    <t xml:space="preserve">model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">std_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robust_std_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robust_p_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sGARCH-Normal</t>
   </si>
   <si>
     <t xml:space="preserve">mu</t>
@@ -125,13 +134,19 @@
     <t xml:space="preserve">beta1</t>
   </si>
   <si>
-    <t xml:space="preserve">Log-Likelihood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIC</t>
+    <t xml:space="preserve">sGARCH-Student-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eGARCH-Student-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gamma1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gjrGARCH-Student-t</t>
   </si>
 </sst>
 </file>
@@ -784,11 +799,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -807,38 +824,56 @@
       <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.00115144547359355</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.00026485051915453</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>4.34752960752826</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.0000137679489848885</v>
       </c>
+      <c r="F2" s="3" t="n">
+        <v>0.000274618230390721</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.000027541663901065</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.00000980701419613725</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.000000479286724104228</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>20.4616854649297</v>
-      </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.000000749936370322581</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -846,68 +881,438 @@
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.0783725569418704</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.00538531877837568</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>14.5530023694362</v>
-      </c>
       <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.00643831349553319</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.886137081631381</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.00659940568331388</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>134.275285405156</v>
-      </c>
       <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.00979017209495373</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>7675.66903100474</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.000657713773930451</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.000219646675780176</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.00274969717198759</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.000193763910040345</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.000687771342710031</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>-5.50730009404504</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.00000884290824540131</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.0000035461110392847</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0126422239387758</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.00000924162765209283</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.338639867080946</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.118747134504418</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.0104161237588472</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.0404943076841755</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.00336309715541194</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>-5.49878270401727</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="C9" s="3" t="n">
+        <v>0.870389781704128</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.00650857002910322</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.0299029357830467</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>3.64991548838201</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.0310982061601767</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.636439903965281</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.00000000975732583619049</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.000477061606634165</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.000227106074721836</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0356750936358901</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.000233082498417961</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.0406826359577523</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.303887432495854</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.0421271144541805</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.000000000000544897460486027</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.0498889973152564</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.00000000112017328746106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0.0479855978507847</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.0229581654082832</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0366059373078544</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.0349596670409652</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.169877097854679</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.962670131038682</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.00507081632066437</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.00589238332842345</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.240236026554501</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.0294125927316405</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.000000000000000222044604925031</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.0283020397822366</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>3.59643928437455</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.275832531666114</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.260435519677593</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.000528530175669506</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.00022563113972867</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.0191574841319364</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.000214444743752422</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.0137149040579396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.0000106950047979249</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.00000154362184456658</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.00000000000425282031812912</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.00000215496120774048</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.000000694238109888445</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0.0845138861444727</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.00548261565805107</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.0171011591291512</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.000000773261965125727</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.85941568629697</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.0113246875348425</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.0119613029307723</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0.0836252556952991</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.0274411668451351</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.00230801102677414</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.0298011008683515</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.00501431090561022</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>3.68631997517378</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.197455058835562</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.267201347784709</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/output/tables/report_tables.xlsx
+++ b/output/tables/report_tables.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -98,28 +98,19 @@
     <t xml:space="preserve">Distribution fit remains a limitation</t>
   </si>
   <si>
-    <t xml:space="preserve">model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">std_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">robust_std_error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">robust_p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sGARCH-Normal</t>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StdError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr_z</t>
   </si>
   <si>
     <t xml:space="preserve">mu</t>
@@ -134,19 +125,13 @@
     <t xml:space="preserve">beta1</t>
   </si>
   <si>
-    <t xml:space="preserve">sGARCH-Student-t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eGARCH-Student-t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gjrGARCH-Student-t</t>
+    <t xml:space="preserve">Log-Likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIC</t>
   </si>
 </sst>
 </file>
@@ -799,13 +784,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,56 +807,38 @@
       <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.00115144547359355</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.00115144547359355</v>
+        <v>0.00026485051915453</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.00026485051915453</v>
+        <v>4.34752960752826</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.0000137679489848885</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0.000274618230390721</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.000027541663901065</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.00000980701419613725</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.00000980701419613725</v>
+        <v>0.000000479286724104228</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.000000479286724104228</v>
+        <v>20.4616854649297</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.000000749936370322581</v>
-      </c>
-      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,438 +846,68 @@
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
+      <c r="B4" s="3" t="n">
+        <v>0.0783725569418704</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0783725569418704</v>
+        <v>0.00538531877837568</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.00538531877837568</v>
+        <v>14.5530023694362</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.00643831349553319</v>
-      </c>
-      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0.886137081631381</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.886137081631381</v>
+        <v>0.00659940568331388</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.00659940568331388</v>
+        <v>134.275285405156</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0.00979017209495373</v>
-      </c>
-      <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.000657713773930451</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.000219646675780176</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.00274969717198759</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.000193763910040345</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.000687771342710031</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7675.66903100474</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0.00000884290824540131</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.0000035461110392847</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0126422239387758</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.00000924162765209283</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.338639867080946</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-5.50730009404504</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0.118747134504418</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.0104161237588472</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.0404943076841755</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.00336309715541194</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0.870389781704128</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0.00650857002910322</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.0299029357830467</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>3.64991548838201</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0.0310982061601767</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.636439903965281</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.00000000975732583619049</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>0.000477061606634165</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0.000227106074721836</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0356750936358901</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.000233082498417961</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.0406826359577523</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>-0.303887432495854</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0.0421271144541805</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.000000000000544897460486027</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>0.0498889973152564</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.00000000112017328746106</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>-0.0479855978507847</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0.0229581654082832</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0366059373078544</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.0349596670409652</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.169877097854679</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0.962670131038682</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.00507081632066437</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.00589238332842345</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>0.240236026554501</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0.0294125927316405</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.000000000000000222044604925031</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.0283020397822366</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>3.59643928437455</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0.275832531666114</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.260435519677593</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0.000528530175669506</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0.00022563113972867</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.0191574841319364</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.000214444743752422</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.0137149040579396</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>0.0000106950047979249</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0.00000154362184456658</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.00000000000425282031812912</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.00000215496120774048</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0.000000694238109888445</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>0.0845138861444727</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0.00548261565805107</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.0171011591291512</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.000000773261965125727</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0.85941568629697</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0.0113246875348425</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.0119613029307723</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>0.0836252556952991</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0.0274411668451351</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.00230801102677414</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0.0298011008683515</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0.00501431090561022</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>3.68631997517378</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0.197455058835562</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.267201347784709</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="3" t="n">
+        <v>-5.49878270401727</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
